--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>74560539</v>
       </c>
       <c r="B5" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>74552073</v>
       </c>
       <c r="B6" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103181</v>
+        <v>103191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2195761</v>
       </c>
       <c r="B2" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483933.0905861623</v>
+        <v>483933</v>
       </c>
       <c r="R2" t="n">
-        <v>6432136.407659647</v>
+        <v>6432136</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1991-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4217780</v>
+        <v>74560539</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483933.0905861623</v>
+        <v>483928</v>
       </c>
       <c r="R3" t="n">
-        <v>6432136.407659647</v>
+        <v>6432132</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1991-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1991-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E6h 4513. SOM: Lathraea squamaria. LEG: Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,31 +872,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3801471</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483933.0905861623</v>
+        <v>483933</v>
       </c>
       <c r="R4" t="n">
-        <v>6432136.407659647</v>
+        <v>6432136</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -982,19 +956,9 @@
           <t>1991-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1991-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,38 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74560539</v>
+        <v>74552073</v>
       </c>
       <c r="B5" t="n">
-        <v>107084</v>
+        <v>102240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Äskebäck södra gdn 200 m OSO, Sm</t>
+          <t>Äskebäck 200 m SO, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1101,7 +1065,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E6h 4513. SOM: Lathraea squamaria. LEG: Jörgen Josefsson</t>
+          <t>Smålands flora 2007: KOO: 7E6h 4513. SOM: Lathyrus vernus. LEG: Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1079,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Lövskogsslänt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1137,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74552073</v>
+        <v>4217780</v>
       </c>
       <c r="B6" t="n">
-        <v>101762</v>
+        <v>103683</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,37 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Äskebäck 200 m SO, Sm</t>
+          <t>Äskebäck södra gdn 200 m OSO, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483928</v>
+        <v>483933</v>
       </c>
       <c r="R6" t="n">
-        <v>6432132</v>
+        <v>6432136</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,17 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1991-06-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7E6h 4513. SOM: Lathyrus vernus. LEG: Jörgen Josefsson</t>
+          <t>1991-06-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1185,28 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Lövskogsslänt</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>75015922</v>
       </c>
       <c r="B7" t="n">
-        <v>103191</v>
+        <v>103682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46815-2025 artfynd.xlsx
+++ b/artfynd/A 46815-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2195761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74560539</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3801471</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4217780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,8 +1341,21 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75015922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>